--- a/fixtures/xlsx/hyperlinks/input.xlsx
+++ b/fixtures/xlsx/hyperlinks/input.xlsx
@@ -10,10 +10,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>https://example.com</t>
+    <t>Description</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>https://example.com</t>
   </si>
   <si>
     <t>URL</t>
@@ -25,5 +25,5 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r="1"><c r="A1" t="s"><v>1</v></c><c r="B1" t="s"><v>2</v></c></row><row r="2"><c r="A2" t="s"><v>3</v></c><c r="B2" t="s"><v>0</v></c></row></sheetData><hyperlinks><hyperlink ref="B2" r:id="rId1"/></hyperlinks></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s"><v>2</v></c></row><row r="2"><c r="A2" t="s"><v>3</v></c><c r="B2" t="s"><v>1</v></c></row></sheetData><hyperlinks><hyperlink ref="B2" r:id="rId1"/></hyperlinks></worksheet>
 </file>
--- a/fixtures/xlsx/hyperlinks/input.xlsx
+++ b/fixtures/xlsx/hyperlinks/input.xlsx
@@ -10,6 +10,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
+    <t>Example site</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -18,12 +21,9 @@
   <si>
     <t>URL</t>
   </si>
-  <si>
-    <t>Example site</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s"><v>2</v></c></row><row r="2"><c r="A2" t="s"><v>3</v></c><c r="B2" t="s"><v>1</v></c></row></sheetData><hyperlinks><hyperlink ref="B2" r:id="rId1"/></hyperlinks></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r="1"><c r="A1" t="s"><v>1</v></c><c r="B1" t="s"><v>3</v></c></row><row r="2"><c r="A2" t="s"><v>0</v></c><c r="B2" t="s"><v>2</v></c></row></sheetData><hyperlinks><hyperlink ref="B2" r:id="rId1"/></hyperlinks></worksheet>
 </file>